--- a/assets/downloads/tables/references_2026-03-23.xlsx
+++ b/assets/downloads/tables/references_2026-03-23.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avian malaria and related parasites from resident and migratory birds in the Brazilian Atlantic forest, with description of a new Haemoproteus species</t>
+          <t>Avian malaria and related parasites from resident and migratory birds in the Brazilian Atlantic forest, with description of a new Haemoproteus species</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Blood parasites in vectors reveal a united blackfly community in the upper canopy</t>
+          <t>Blood parasites in vectors reveal a united blackfly community in the upper canopy</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Geographic and host distribution of haemosporidian parasite lineages from birds of the family Turdidae</t>
+          <t>Geographic and host distribution of haemosporidian parasite lineages from birds of the family Turdidae</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Diversity, abundance, and host relationships in the avian malaria community of New Mexico pine forests </t>
+          <t>Diversity, abundance, and host relationships in the avian malaria community of New Mexico pine forests</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Molecular detection of blood protozoa and identification of black flies of the Simulium varicorne species group (Diptera: Simuliidae) in Thailand</t>
+          <t>Molecular detection of blood protozoa and identification of black flies of the Simulium varicorne species group (Diptera: Simuliidae) in Thailand</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
